--- a/new-stats/fc-voluntari.xlsx
+++ b/new-stats/fc-voluntari.xlsx
@@ -569,22 +569,62 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>CFR Cluj</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>FC Voluntari</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>3</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="M3" t="n">
+        <v>9</v>
+      </c>
+      <c r="N3" t="n">
+        <v>21</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P3" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr"/>

--- a/new-stats/fc-voluntari.xlsx
+++ b/new-stats/fc-voluntari.xlsx
@@ -627,22 +627,62 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>FC Voluntari</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>UTA Arad</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M4" t="n">
+        <v>9</v>
+      </c>
+      <c r="N4" t="n">
+        <v>18</v>
+      </c>
+      <c r="O4" t="n">
+        <v>3</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>

--- a/new-stats/fc-voluntari.xlsx
+++ b/new-stats/fc-voluntari.xlsx
@@ -685,22 +685,62 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>08/08/2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Dinamo Bucuresti</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>FC Voluntari</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="M5" t="n">
+        <v>5</v>
+      </c>
+      <c r="N5" t="n">
+        <v>22</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2</v>
+      </c>
+      <c r="P5" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>

--- a/new-stats/fc-voluntari.xlsx
+++ b/new-stats/fc-voluntari.xlsx
@@ -743,22 +743,62 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>FC Voluntari</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Petrolul</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="M6" t="n">
+        <v>16</v>
+      </c>
+      <c r="N6" t="n">
+        <v>19</v>
+      </c>
+      <c r="O6" t="n">
+        <v>5</v>
+      </c>
+      <c r="P6" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
